--- a/3.语义搜索/milvus数据类型，索引类型说明.xlsx
+++ b/3.语义搜索/milvus数据类型，索引类型说明.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20170" windowHeight="7150"/>
+    <workbookView windowWidth="21600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="166">
   <si>
     <t>DataType</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>FLOAT16_VECTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>说明</t>
@@ -1137,12 +1140,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1153,7 +1150,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1161,6 +1158,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1633,7 +1636,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1656,7 +1659,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1674,15 +1683,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2030,7 +2030,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -2044,7 +2044,7 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" spans="1:4">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:4">
+    <row r="2" ht="42" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="28" spans="1:4">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="28" spans="1:4">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:4">
+    <row r="5" ht="28" spans="1:6">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:4">
+    <row r="6" ht="28" spans="1:6">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="28" spans="1:4">
+    <row r="7" ht="28" spans="1:6">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -2141,263 +2141,269 @@
       <c r="D7" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" ht="28" spans="1:4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:6">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" ht="28" spans="1:4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:6">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" ht="28" spans="1:4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:6">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" ht="56" spans="1:10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" ht="56" spans="1:20">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" ht="196" spans="1:10">
+    <row r="20" ht="196" spans="1:20">
       <c r="A20" s="4"/>
       <c r="B20" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" ht="154" spans="1:10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" ht="154" spans="1:20">
       <c r="A21" s="4"/>
       <c r="B21" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" ht="280" spans="1:10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" ht="280" spans="1:20">
       <c r="A22" s="4"/>
       <c r="B22" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>84</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" s="4"/>
       <c r="B23" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -2406,55 +2412,55 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" ht="84" spans="1:10">
+    <row r="24" ht="84" spans="1:20">
       <c r="A24" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="15" t="s">
-        <v>91</v>
+      <c r="I24" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:20">
       <c r="A25" s="4"/>
       <c r="B25" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>95</v>
+        <v>62</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>96</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" ht="112" spans="1:10">
+    <row r="26" ht="112" spans="1:20">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2462,293 +2468,300 @@
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" ht="28" spans="1:2">
-      <c r="A30" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="30" ht="28" spans="1:20">
+      <c r="A30" s="10" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="31" ht="28" spans="1:2">
-      <c r="A31" s="1" t="s">
+      <c r="B30" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="1" t="s">
+    </row>
+    <row r="31" ht="28" spans="1:20">
+      <c r="A31" s="10" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
+      <c r="B31" s="10" t="s">
         <v>105</v>
       </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="A32" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="10"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="B37" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" ht="28" spans="1:3">
+      <c r="A38" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" ht="28" spans="1:3">
+      <c r="A39" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" ht="28" spans="1:3">
+      <c r="A40" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="12"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" ht="28" spans="1:3">
+      <c r="A46" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" ht="28" spans="1:3">
+      <c r="A47" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" ht="30" spans="1:3">
+      <c r="A48" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" ht="42" spans="1:4">
+      <c r="A50" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="C54"/>
+    </row>
+    <row r="55" ht="23" spans="1:4">
+      <c r="A55" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" ht="28.5" spans="1:4">
+      <c r="A57" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" ht="28" spans="1:4">
+      <c r="A58" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" ht="28" spans="1:4">
+      <c r="A59" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="38" ht="28" spans="1:3">
-      <c r="A38" s="10" t="s">
+    <row r="64" spans="1:4">
+      <c r="A64" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" ht="28" spans="1:3">
-      <c r="A39" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" ht="28" spans="1:3">
-      <c r="A40" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" s="10"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="3"/>
-    </row>
-    <row r="46" ht="28" spans="1:3">
-      <c r="A46" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" s="3"/>
-    </row>
-    <row r="47" ht="28" spans="1:3">
-      <c r="A47" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" s="3"/>
-    </row>
-    <row r="48" ht="30" spans="1:3">
-      <c r="A48" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="50" ht="42" spans="1:3">
-      <c r="A50" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C50" s="3"/>
-    </row>
-    <row r="54" spans="3:3">
-      <c r="C54"/>
-    </row>
-    <row r="55" ht="23" spans="1:3">
-      <c r="A55" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="57" ht="28.5" spans="1:3">
-      <c r="A57" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="58" ht="28" spans="1:3">
-      <c r="A58" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="59" ht="28" spans="1:3">
-      <c r="A59" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" ht="28" spans="1:4">
-      <c r="A66" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="B66" s="17" t="s">
+      <c r="D65" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" ht="28" spans="1:5">
+      <c r="A66" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="B66" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="12" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="67" ht="28" spans="1:4">
-      <c r="A67" s="17" t="s">
+      <c r="D66" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="17" t="s">
+    </row>
+    <row r="67" ht="28" spans="1:5">
+      <c r="A67" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="B67" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="C67" s="12" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="68" ht="28" spans="1:4">
-      <c r="A68" s="17" t="s">
+      <c r="D67" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="17" t="s">
+    </row>
+    <row r="68" ht="28" spans="1:5">
+      <c r="A68" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="B68" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="C68" s="12" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="69" ht="28" spans="1:4">
-      <c r="A69" s="17" t="s">
+      <c r="D68" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="E68" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" ht="28" spans="1:5">
+      <c r="A69" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="B69" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="C69" s="12" t="s">
         <v>164</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/3.语义搜索/milvus数据类型，索引类型说明.xlsx
+++ b/3.语义搜索/milvus数据类型，索引类型说明.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="10480"/>
+    <workbookView windowWidth="10800" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="166">
   <si>
     <t>DataType</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>用于加速或节省空间</t>
+  </si>
+  <si>
+    <t>字段类型</t>
   </si>
   <si>
     <t>索引类型</t>
@@ -323,9 +326,6 @@
   </si>
   <si>
     <t>高压缩，高速</t>
-  </si>
-  <si>
-    <t>nprobe, m, nbits</t>
   </si>
   <si>
     <r>
@@ -1140,6 +1140,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1158,12 +1164,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1636,7 +1636,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1663,9 +1663,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2244,9 +2241,11 @@
       </c>
     </row>
     <row r="18" spans="1:20">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>23</v>
@@ -2255,22 +2254,22 @@
         <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" ht="56" spans="1:20">
@@ -2278,75 +2277,73 @@
         <v>4</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J19" s="3"/>
     </row>
     <row r="20" ht="196" spans="1:20">
       <c r="A20" s="4"/>
       <c r="B20" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="154" spans="1:20">
       <c r="A21" s="4"/>
       <c r="B21" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="E21" s="3"/>
       <c r="F21" s="7" t="s">
         <v>72</v>
       </c>
@@ -2389,6 +2386,9 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
         <v>84</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>22</v>
@@ -2426,7 +2426,7 @@
         <v>90</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>91</v>
@@ -2450,7 +2450,7 @@
         <v>95</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>96</v>
@@ -2487,26 +2487,26 @@
       </c>
     </row>
     <row r="30" ht="28" spans="1:20">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="31" ht="28" spans="1:20">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:20">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="10"/>
+      <c r="B32" s="3"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
@@ -2516,90 +2516,90 @@
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="38" ht="28" spans="1:3">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="39" ht="28" spans="1:3">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="40" ht="28" spans="1:3">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="12"/>
+      <c r="C41" s="11"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>122</v>
       </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" ht="28" spans="1:3">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="11" t="s">
         <v>124</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" ht="28" spans="1:3">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="11" t="s">
         <v>126</v>
       </c>
       <c r="C47" s="3"/>
     </row>
     <row r="48" ht="30" spans="1:3">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="12" t="s">
         <v>128</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -2607,10 +2607,10 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -2618,10 +2618,10 @@
       </c>
     </row>
     <row r="50" ht="42" spans="1:4">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="11" t="s">
         <v>134</v>
       </c>
       <c r="C50" s="3"/>
@@ -2630,53 +2630,53 @@
       <c r="C54"/>
     </row>
     <row r="55" ht="23" spans="1:4">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="57" ht="28.5" spans="1:4">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="11" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="58" ht="28" spans="1:4">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="11" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="59" ht="28" spans="1:4">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -2684,66 +2684,66 @@
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="66" ht="28" spans="1:5">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="67" ht="28" spans="1:5">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="68" ht="28" spans="1:5">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="11" t="s">
         <v>161</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -2751,16 +2751,16 @@
       </c>
     </row>
     <row r="69" ht="28" spans="1:5">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="11" t="s">
         <v>165</v>
       </c>
     </row>
